--- a/data/trans_orig/IP3106-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3106-Habitat-trans_orig.xlsx
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16893</t>
+          <t>16825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>20591</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35780</t>
+          <t>36731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15086</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29220</t>
+          <t>29600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39006</t>
+          <t>38664</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60469</t>
+          <t>58952</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89753</t>
+          <t>90102</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>105884</t>
+          <t>105757</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>103974</t>
+          <t>103587</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119475</t>
+          <t>119414</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>199251</t>
+          <t>200483</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>222584</t>
+          <t>222461</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13756</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27617</t>
+          <t>27120</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27264</t>
+          <t>27306</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44372</t>
+          <t>44089</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31990</t>
+          <t>31914</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50724</t>
+          <t>49496</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>63358</t>
+          <t>63423</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>87508</t>
+          <t>88057</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>126468</t>
+          <t>125795</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>144904</t>
+          <t>143805</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139617</t>
+          <t>140388</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159666</t>
+          <t>159411</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>273527</t>
+          <t>271856</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>299245</t>
+          <t>298207</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,12%</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20090</t>
+          <t>19287</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>11599</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23550</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13819</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27754</t>
+          <t>26970</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28733</t>
+          <t>28884</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47534</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96661</t>
+          <t>95373</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109907</t>
+          <t>109643</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>102619</t>
+          <t>102795</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>117890</t>
+          <t>118084</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>202835</t>
+          <t>204320</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>222560</t>
+          <t>224484</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21960</t>
+          <t>20974</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>16377</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16991</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32805</t>
+          <t>33584</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24297</t>
+          <t>24407</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41632</t>
+          <t>43090</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30864</t>
+          <t>31074</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49108</t>
+          <t>47823</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>60994</t>
+          <t>60786</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>85321</t>
+          <t>85050</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>139496</t>
+          <t>140004</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>159748</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>132686</t>
+          <t>133317</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>151900</t>
+          <t>152587</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>279329</t>
+          <t>279104</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>306222</t>
+          <t>306839</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,45%</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4252,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24700</t>
+          <t>24719</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>42623</t>
+          <t>43801</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>24999</t>
+          <t>24627</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>44372</t>
+          <t>42788</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>55178</t>
+          <t>54611</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>82079</t>
+          <t>80981</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -4365,12 +4365,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>96917</t>
+          <t>97225</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>127736</t>
+          <t>126981</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>105912</t>
+          <t>105849</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>136995</t>
+          <t>137523</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>212908</t>
+          <t>212776</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>257466</t>
+          <t>258197</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>471486</t>
+          <t>471538</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>504997</t>
+          <t>503844</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>497848</t>
+          <t>499662</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>532869</t>
+          <t>533140</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>979215</t>
+          <t>979893</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1030657</t>
+          <t>1027893</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5392,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5407,12 +5407,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18553</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25481</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114374</t>
+          <t>114563</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125984</t>
+          <t>125515</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117911</t>
+          <t>118963</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>131413</t>
+          <t>131717</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>237505</t>
+          <t>237213</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>254481</t>
+          <t>254732</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>14689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>20622</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15969</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>31875</t>
+          <t>31085</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170235</t>
+          <t>170267</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>181648</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>180121</t>
+          <t>180117</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>193887</t>
+          <t>193516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>353445</t>
+          <t>354029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>372260</t>
+          <t>371989</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1776</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13590</t>
+          <t>13189</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26724</t>
+          <t>27279</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -7095,12 +7095,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>122068</t>
+          <t>122151</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>133228</t>
+          <t>133211</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127493</t>
+          <t>127092</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>139473</t>
+          <t>139464</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>254835</t>
+          <t>254286</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>270205</t>
+          <t>270190</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,91%</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>11472</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7679,12 +7679,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7699,12 +7699,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18791</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7812,12 +7812,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17530</t>
+          <t>17685</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>15656</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32656</t>
+          <t>31891</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>164532</t>
+          <t>164385</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>178394</t>
+          <t>178632</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7925,12 +7925,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>165999</t>
+          <t>165714</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>180005</t>
+          <t>180277</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7960,12 +7960,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>334386</t>
+          <t>335396</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>355321</t>
+          <t>356017</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7975,12 +7975,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26939</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>26107</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>26939</t>
+          <t>27401</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>48615</t>
+          <t>47944</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -8572,12 +8572,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>25961</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>45231</t>
+          <t>44887</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>36811</t>
+          <t>37679</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>60017</t>
+          <t>59484</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8642,12 +8642,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>69091</t>
+          <t>68323</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>96673</t>
+          <t>97743</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8657,12 +8657,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>586091</t>
+          <t>587242</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>609739</t>
+          <t>611351</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8720,12 +8720,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>607228</t>
+          <t>607965</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>634470</t>
+          <t>634885</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1203301</t>
+          <t>1202947</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1237696</t>
+          <t>1237592</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11577</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>12491</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26647</t>
+          <t>27213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>11456</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25067</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28216</t>
+          <t>28846</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48361</t>
+          <t>49182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -9712,12 +9712,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88622</t>
+          <t>88076</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>103456</t>
+          <t>103045</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9727,12 +9727,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9747,12 +9747,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>106245</t>
+          <t>105576</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>122139</t>
+          <t>121530</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>199595</t>
+          <t>198718</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>221235</t>
+          <t>221329</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9797,12 +9797,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -10281,12 +10281,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10331,12 +10331,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22142</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10366,12 +10366,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -10394,12 +10394,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29778</t>
+          <t>29981</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10429,12 +10429,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17262</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31885</t>
+          <t>31514</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10444,12 +10444,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10464,12 +10464,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>37983</t>
+          <t>36673</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>57514</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10479,12 +10479,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -10507,12 +10507,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>156333</t>
+          <t>156164</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171402</t>
+          <t>171046</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>165615</t>
+          <t>164253</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183598</t>
+          <t>182184</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10557,12 +10557,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10577,12 +10577,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>325416</t>
+          <t>324704</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>348657</t>
+          <t>349477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10592,12 +10592,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11126,12 +11126,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -11189,12 +11189,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12976</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16444</t>
+          <t>16935</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11259,12 +11259,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12174</t>
+          <t>11748</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26113</t>
+          <t>24783</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -11302,12 +11302,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>130059</t>
+          <t>129499</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>139558</t>
+          <t>139725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11337,12 +11337,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>137675</t>
+          <t>137059</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>149877</t>
+          <t>149822</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11372,12 +11372,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>271837</t>
+          <t>272590</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>287245</t>
+          <t>287412</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11387,12 +11387,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -11871,12 +11871,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11921,12 +11921,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11956,12 +11956,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -11984,12 +11984,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28388</t>
+          <t>29053</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11999,12 +11999,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24073</t>
+          <t>24411</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12034,12 +12034,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12054,12 +12054,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28777</t>
+          <t>28598</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49013</t>
+          <t>48053</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12069,12 +12069,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -12097,12 +12097,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>156426</t>
+          <t>156358</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>172637</t>
+          <t>172515</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>160755</t>
+          <t>160228</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>174706</t>
+          <t>174697</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>323020</t>
+          <t>323229</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>344213</t>
+          <t>344048</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -12558,7 +12558,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12588,12 +12588,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24808</t>
+          <t>24576</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12681,12 +12681,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>32355</t>
+          <t>31679</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12716,12 +12716,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>30181</t>
+          <t>31093</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>52449</t>
+          <t>52231</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12751,12 +12751,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -12779,12 +12779,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>60034</t>
+          <t>59004</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>84867</t>
+          <t>84980</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>56995</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>82864</t>
+          <t>83322</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12849,12 +12849,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>121661</t>
+          <t>121350</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>158124</t>
+          <t>158034</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -12892,12 +12892,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>547148</t>
+          <t>547300</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>575405</t>
+          <t>576086</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12907,12 +12907,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12927,12 +12927,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>588596</t>
+          <t>587283</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>618102</t>
+          <t>616983</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1143914</t>
+          <t>1143461</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1184135</t>
+          <t>1185296</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -13580,12 +13580,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>549</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13595,12 +13595,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13615,12 +13615,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13650,12 +13650,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13665,12 +13665,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -13693,12 +13693,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -13728,12 +13728,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22273</t>
+          <t>21929</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13763,12 +13763,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>15068</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29353</t>
+          <t>30959</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>17949</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30845</t>
+          <t>31367</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13821,12 +13821,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13841,12 +13841,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>18420</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36454</t>
+          <t>36506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13856,12 +13856,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -13876,12 +13876,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39332</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61793</t>
+          <t>61637</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -13891,12 +13891,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -13919,12 +13919,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73784</t>
+          <t>72747</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88477</t>
+          <t>88489</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -13934,12 +13934,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82550</t>
+          <t>82573</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>105203</t>
+          <t>105594</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13989,12 +13989,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>161764</t>
+          <t>162568</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190059</t>
+          <t>189126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14004,12 +14004,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,5%</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14380,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -14488,12 +14488,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>20736</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14503,12 +14503,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14523,12 +14523,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>14867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34300</t>
+          <t>32754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14558,12 +14558,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28193</t>
+          <t>27292</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48592</t>
+          <t>48929</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14573,12 +14573,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -14601,12 +14601,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31534</t>
+          <t>31284</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50427</t>
+          <t>50217</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14616,12 +14616,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52150</t>
+          <t>51835</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>80025</t>
+          <t>81486</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14651,12 +14651,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14671,12 +14671,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>88615</t>
+          <t>89446</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>123669</t>
+          <t>124291</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14686,12 +14686,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -14714,12 +14714,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120676</t>
+          <t>121016</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141867</t>
+          <t>141791</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14729,12 +14729,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14749,12 +14749,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141702</t>
+          <t>142024</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>172257</t>
+          <t>172586</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14764,12 +14764,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>269909</t>
+          <t>269122</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>307535</t>
+          <t>306067</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14799,12 +14799,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,58%</t>
         </is>
       </c>
     </row>
@@ -15175,7 +15175,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15190,7 +15190,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -15283,12 +15283,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15298,12 +15298,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15318,12 +15318,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18123</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15333,12 +15333,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15353,12 +15353,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>21447</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15368,12 +15368,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -15396,12 +15396,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38853</t>
+          <t>40529</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113582</t>
+          <t>117922</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15411,12 +15411,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>31123</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56919</t>
+          <t>54897</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15446,12 +15446,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15466,12 +15466,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77490</t>
+          <t>77963</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>162779</t>
+          <t>174966</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15481,12 +15481,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>47,12%</t>
         </is>
       </c>
     </row>
@@ -15509,12 +15509,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>73812</t>
+          <t>67849</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>144807</t>
+          <t>143157</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15524,12 +15524,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15544,12 +15544,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>115483</t>
+          <t>117647</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142950</t>
+          <t>142633</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15559,12 +15559,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15579,12 +15579,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>200051</t>
+          <t>183040</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>279085</t>
+          <t>278749</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15594,12 +15594,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -15970,7 +15970,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16020,7 +16020,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16035,12 +16035,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>552</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16055,7 +16055,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -16078,12 +16078,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16093,12 +16093,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16113,12 +16113,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16690</t>
+          <t>15455</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16128,12 +16128,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16148,12 +16148,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>22696</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16163,12 +16163,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -16191,12 +16191,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28830</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48017</t>
+          <t>47871</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16206,12 +16206,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16226,12 +16226,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25515</t>
+          <t>25711</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44549</t>
+          <t>44502</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16241,12 +16241,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16261,12 +16261,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>59020</t>
+          <t>58587</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>85453</t>
+          <t>85382</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16276,12 +16276,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -16304,12 +16304,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>109524</t>
+          <t>110648</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>129558</t>
+          <t>130778</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16319,12 +16319,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16339,12 +16339,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>120835</t>
+          <t>120532</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141511</t>
+          <t>140669</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16354,12 +16354,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16374,12 +16374,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>238058</t>
+          <t>238132</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>267156</t>
+          <t>266285</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16389,12 +16389,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,9%</t>
         </is>
       </c>
     </row>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16609,7 +16609,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16624,7 +16624,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -16760,12 +16760,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -16795,12 +16795,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16810,12 +16810,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16830,12 +16830,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16850,7 +16850,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -16873,12 +16873,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>22247</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>39865</t>
+          <t>39751</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16888,12 +16888,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16908,12 +16908,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>44196</t>
+          <t>45121</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>71293</t>
+          <t>70735</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16943,12 +16943,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>71179</t>
+          <t>70615</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>103903</t>
+          <t>102454</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16958,12 +16958,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -16986,12 +16986,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>139015</t>
+          <t>136470</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>246316</t>
+          <t>236877</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17001,12 +17001,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17021,12 +17021,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>147044</t>
+          <t>143449</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>192030</t>
+          <t>189261</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17036,12 +17036,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17056,12 +17056,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>297802</t>
+          <t>296794</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>415203</t>
+          <t>400601</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17071,12 +17071,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -17099,12 +17099,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>386255</t>
+          <t>389174</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>479913</t>
+          <t>481303</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17134,12 +17134,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>491430</t>
+          <t>490860</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>538922</t>
+          <t>540340</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17149,12 +17149,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17169,12 +17169,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>898558</t>
+          <t>903231</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1004536</t>
+          <t>1004248</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17184,12 +17184,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
